--- a/data/August.xlsx
+++ b/data/August.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0598BF7-DC2C-4873-A654-0D5748095FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949BB654-CE13-43C8-B64A-BD08E2D36C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,11 +50,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="76">
   <si>
     <t>Ad name</t>
   </si>
   <si>
+    <t>วันนี้เคททำไรอะ - ทองต่างประเทศ</t>
+  </si>
+  <si>
+    <t>Main Account-ลูกค้านำจี้มาขายได้ราคาเกินคาด</t>
+  </si>
+  <si>
+    <t>Main Account-ใครบอก "ทองชุบ" ไม่มีราคา</t>
+  </si>
+  <si>
+    <t>Main Account-ลูกค้าถึงกับตกใจ ขายตะขออะไร ได้ราคาเท่ากรอบพระ</t>
+  </si>
+  <si>
+    <t>Main Account-เคยเห็นแต่ในหนังจีน…วันนี้ลูกค้ายก</t>
+  </si>
+  <si>
+    <t>Main Account-ของหน้าตาแบบนี้ มีค่าจริงมั้ยย</t>
+  </si>
+  <si>
+    <t>Main Account-พี่วินเอากำไลข้อเท้าหลานมาขายกับเฮียหลอม</t>
+  </si>
+  <si>
+    <t>Main Account-ของที่เก็บมาจากกองขยะ ใครจะคิดว่าหลอมแล้วมีเงินอยู่จริง</t>
+  </si>
+  <si>
+    <t>Main Account-เอามาขายเป็นกอง เฮียหลอมก็รับไหว</t>
+  </si>
+  <si>
+    <t>Main Account - ลูกค้าเอาเหรียญมาให้เช็ก เพราะไม่แน่ใจว่ามีค่าไหม</t>
+  </si>
+  <si>
+    <t>Main Account - ลูกค้าถึงกับตกใจ ขายตะขออะไร</t>
+  </si>
+  <si>
+    <t>Main Account - ตอนแรกนึกว่าเศษดิน ที่ไหนได้</t>
+  </si>
+  <si>
+    <t>Main Account - ใครบอก "ทองชุบ" ไม่มีราคา</t>
+  </si>
+  <si>
+    <t>สาขาหน้าเมือง-กรอบพระ5องค์นี้ ลูกค้ารับเงินไปสูงถึง 39,xxx บาทค่ะ</t>
+  </si>
+  <si>
+    <t>สาขาแยกคีรีชลบุรี-ทำไมลูกค้า ถึงเลือกที่จะขายแบบหลอม</t>
+  </si>
+  <si>
+    <t>สาขาหน้าเมือง-ร้านอื่นรับซื้อแค่1,500บาท แล้วเฮียหลอมล่ะ.</t>
+  </si>
+  <si>
+    <t>สาขาแยกคีรีชลบุรี-เมื่อขาประจำ นำทองเข้ามาหลอม</t>
+  </si>
+  <si>
     <t>สาขาหัวทะเล-ไม่ว่าจะเป็นทองคำชนิดไหนเราก็รับซื้อหมด</t>
   </si>
   <si>
@@ -70,55 +121,13 @@
     <t>สาขาด่านขุนทด-เครื่องประดับเก่าจะขายได้ราคามั้ย</t>
   </si>
   <si>
-    <t>สาขาหน้าเมือง-กรอบพระ5องค์นี้ ลูกค้ารับเงินไปสูงถึง 39,xxx บาทค่ะ</t>
-  </si>
-  <si>
-    <t>สาขาหน้าเมือง-ร้านอื่นรับซื้อแค่1,500บาท แล้วเฮียหลอมล่ะ.</t>
-  </si>
-  <si>
-    <t>สาขาแยกคีรีชลบุรี-ทำไมลูกค้า ถึงเลือกที่จะขายแบบหลอม</t>
-  </si>
-  <si>
-    <t>สาขาแยกคีรีชลบุรี-เมื่อขาประจำ นำทองเข้ามาหลอม</t>
-  </si>
-  <si>
-    <t>Main Account - ลูกค้าเอาเหรียญมาให้เช็ก เพราะไม่แน่ใจว่ามีค่าไหม</t>
-  </si>
-  <si>
-    <t>Main Account - ลูกค้าถึงกับตกใจ ขายตะขออะไร</t>
-  </si>
-  <si>
-    <t>Main Account - ตอนแรกนึกว่าเศษดิน ที่ไหนได้</t>
-  </si>
-  <si>
-    <t>Main Account - ใครบอก "ทองชุบ" ไม่มีราคา</t>
-  </si>
-  <si>
-    <t>Main Account-เคยเห็นแต่ในหนังจีน…วันนี้ลูกค้ายก</t>
-  </si>
-  <si>
-    <t>Main Account-เอามาขายเป็นกอง เฮียหลอมก็รับไหว</t>
-  </si>
-  <si>
-    <t>Main Account-พี่วินเอากำไลข้อเท้าหลานมาขายกับเฮียหลอม</t>
-  </si>
-  <si>
-    <t>Main Account-ของที่เก็บมาจากกองขยะ ใครจะคิดว่าหลอมแล้วมีเงินอยู่จริง</t>
-  </si>
-  <si>
-    <t>Main Account-ของหน้าตาแบบนี้ มีค่าจริงมั้ยย</t>
-  </si>
-  <si>
-    <t>วันนี้เคททำไรอะ - ทองต่างประเทศ</t>
-  </si>
-  <si>
     <t>Primary status</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Not delivering</t>
+    <t>Paused</t>
+  </si>
+  <si>
+    <t>Ended</t>
   </si>
   <si>
     <t>-</t>
@@ -127,15 +136,42 @@
     <t>Secondary status</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>Out of ad group budget</t>
+    <t>Ad group paused;  ; Ad completed; Review not approved</t>
+  </si>
+  <si>
+    <t>Ad group paused; Ad completed; Out of ad group budget</t>
+  </si>
+  <si>
+    <t>Ad group paused; Ad completed</t>
+  </si>
+  <si>
+    <t>Ad group paused;  ; Ad completed; Out of ad group budget</t>
+  </si>
+  <si>
+    <t>Ad group paused;  ; Ad completed</t>
+  </si>
+  <si>
+    <t>Ad completed; Out of ad group budget</t>
   </si>
   <si>
     <t>Campaign name</t>
   </si>
   <si>
+    <t xml:space="preserve">2105 - Video View - KOLs </t>
+  </si>
+  <si>
+    <t>2105 - Main Account - Video view</t>
+  </si>
+  <si>
+    <t>2105 - Main Account - Follower</t>
+  </si>
+  <si>
+    <t>2105 - สาขาหน้าเมือง - Video view</t>
+  </si>
+  <si>
+    <t>2105 - สาขาแยกคีรีชลบุรี - Video view</t>
+  </si>
+  <si>
     <t>2105 - สาขาหัวทะเล - Video view</t>
   </si>
   <si>
@@ -151,76 +187,37 @@
     <t>2105 - สาขาด่านขุนทด - Video view</t>
   </si>
   <si>
-    <t>2105 - สาขาหน้าเมือง - Video view</t>
-  </si>
-  <si>
-    <t>2105 - สาขาแยกคีรีชลบุรี - Video view</t>
-  </si>
-  <si>
-    <t>2105 - Main Account - Follower</t>
-  </si>
-  <si>
-    <t>2105 - Main Account - Video view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2105 - Video View - KOLs </t>
-  </si>
-  <si>
     <t>Spend</t>
   </si>
   <si>
-    <t>325.28</t>
-  </si>
-  <si>
-    <t>305.18</t>
-  </si>
-  <si>
-    <t>310.83</t>
-  </si>
-  <si>
-    <t>246.61</t>
-  </si>
-  <si>
-    <t>243.18</t>
-  </si>
-  <si>
-    <t>464.50</t>
-  </si>
-  <si>
-    <t>462.01</t>
-  </si>
-  <si>
-    <t>472.65</t>
-  </si>
-  <si>
-    <t>456.52</t>
+    <t>4999.61</t>
+  </si>
+  <si>
+    <t>4500.00</t>
+  </si>
+  <si>
+    <t>4499.85</t>
+  </si>
+  <si>
+    <t>4499.44</t>
   </si>
   <si>
     <t>2500.00</t>
   </si>
   <si>
-    <t>413.98</t>
-  </si>
-  <si>
-    <t>1345.71</t>
-  </si>
-  <si>
-    <t>1122.60</t>
-  </si>
-  <si>
-    <t>1090.84</t>
-  </si>
-  <si>
-    <t>1113.74</t>
-  </si>
-  <si>
-    <t>1109.86</t>
-  </si>
-  <si>
-    <t>1091.10</t>
-  </si>
-  <si>
-    <t>1167.22</t>
+    <t>2000.00</t>
+  </si>
+  <si>
+    <t>1999.90</t>
+  </si>
+  <si>
+    <t>1999.74</t>
+  </si>
+  <si>
+    <t>1999.10</t>
+  </si>
+  <si>
+    <t>1000.00</t>
   </si>
   <si>
     <t>Reach</t>
@@ -259,19 +256,19 @@
     <t>Secondary source</t>
   </si>
   <si>
+    <t>Authorized by video code</t>
+  </si>
+  <si>
     <t>TikTok account</t>
   </si>
   <si>
-    <t>Authorized by video code</t>
-  </si>
-  <si>
     <t>Primary source</t>
   </si>
   <si>
+    <t>TikTok creator content</t>
+  </si>
+  <si>
     <t>Your own content</t>
-  </si>
-  <si>
-    <t>TikTok creator content</t>
   </si>
   <si>
     <t>Attribution source</t>
@@ -622,69 +619,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="70.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -692,61 +692,61 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2">
+        <v>139238</v>
+      </c>
+      <c r="G2" s="2">
+        <v>332396</v>
+      </c>
+      <c r="H2" s="2">
+        <v>322634</v>
+      </c>
+      <c r="I2" s="2">
+        <v>78225</v>
+      </c>
+      <c r="J2" s="2">
+        <v>19664</v>
+      </c>
+      <c r="K2" s="2">
+        <v>3061</v>
+      </c>
+      <c r="L2" s="2">
+        <v>4</v>
+      </c>
+      <c r="M2" s="2">
+        <v>7</v>
+      </c>
+      <c r="N2" s="2">
         <v>39</v>
       </c>
-      <c r="F2" s="2">
-        <v>19243</v>
-      </c>
-      <c r="G2" s="2">
-        <v>22917</v>
-      </c>
-      <c r="H2" s="2">
-        <v>22345</v>
-      </c>
-      <c r="I2" s="2">
-        <v>5776</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1389</v>
-      </c>
-      <c r="K2" s="2">
-        <v>33</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>1</v>
-      </c>
       <c r="O2" s="2">
-        <v>40</v>
+        <v>948</v>
       </c>
       <c r="P2" s="2">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -754,49 +754,49 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2">
-        <v>17371</v>
+        <v>108036</v>
       </c>
       <c r="G3" s="2">
-        <v>21183</v>
+        <v>245586</v>
       </c>
       <c r="H3" s="2">
-        <v>20580</v>
+        <v>242643</v>
       </c>
       <c r="I3" s="2">
-        <v>4110</v>
+        <v>57461</v>
       </c>
       <c r="J3" s="2">
-        <v>572</v>
+        <v>5168</v>
       </c>
       <c r="K3" s="2">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="L3" s="2">
         <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O3" s="2">
-        <v>31</v>
+        <v>249</v>
       </c>
       <c r="P3" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>69</v>
@@ -805,10 +805,10 @@
         <v>72</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -816,49 +816,49 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F4" s="2">
-        <v>18151</v>
+        <v>132798</v>
       </c>
       <c r="G4" s="2">
-        <v>22357</v>
+        <v>300576</v>
       </c>
       <c r="H4" s="2">
-        <v>21903</v>
+        <v>293919</v>
       </c>
       <c r="I4" s="2">
-        <v>2469</v>
+        <v>33141</v>
       </c>
       <c r="J4" s="2">
-        <v>506</v>
+        <v>8026</v>
       </c>
       <c r="K4" s="2">
-        <v>10</v>
+        <v>433</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="2">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="O4" s="2">
-        <v>29</v>
+        <v>553</v>
       </c>
       <c r="P4" s="2">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>69</v>
@@ -867,10 +867,10 @@
         <v>72</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -878,49 +878,49 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2">
-        <v>14044</v>
+        <v>114609</v>
       </c>
       <c r="G5" s="2">
-        <v>17632</v>
+        <v>246452</v>
       </c>
       <c r="H5" s="2">
-        <v>17233</v>
+        <v>243790</v>
       </c>
       <c r="I5" s="2">
-        <v>1513</v>
+        <v>38389</v>
       </c>
       <c r="J5" s="2">
-        <v>273</v>
+        <v>5048</v>
       </c>
       <c r="K5" s="2">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O5" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="P5" s="2">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>69</v>
@@ -929,10 +929,10 @@
         <v>72</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -940,49 +940,49 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2">
-        <v>14883</v>
+        <v>122523</v>
       </c>
       <c r="G6" s="2">
-        <v>18065</v>
+        <v>321838</v>
       </c>
       <c r="H6" s="2">
-        <v>17652</v>
+        <v>315758</v>
       </c>
       <c r="I6" s="2">
-        <v>1685</v>
+        <v>32747</v>
       </c>
       <c r="J6" s="2">
-        <v>355</v>
+        <v>10412</v>
       </c>
       <c r="K6" s="2">
-        <v>19</v>
+        <v>212</v>
       </c>
       <c r="L6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O6" s="2">
+        <v>301</v>
+      </c>
+      <c r="P6" s="2">
         <v>29</v>
-      </c>
-      <c r="P6" s="2">
-        <v>1</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>69</v>
@@ -991,10 +991,10 @@
         <v>72</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1002,49 +1002,49 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2">
-        <v>24937</v>
+        <v>118584</v>
       </c>
       <c r="G7" s="2">
-        <v>33915</v>
+        <v>311194</v>
       </c>
       <c r="H7" s="2">
-        <v>33287</v>
+        <v>299597</v>
       </c>
       <c r="I7" s="2">
-        <v>2239</v>
+        <v>47678</v>
       </c>
       <c r="J7" s="2">
-        <v>548</v>
+        <v>10608</v>
       </c>
       <c r="K7" s="2">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2">
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46</v>
+        <v>448</v>
       </c>
       <c r="P7" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>69</v>
@@ -1053,10 +1053,10 @@
         <v>72</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1064,34 +1064,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>24783</v>
+        <v>118229</v>
       </c>
       <c r="G8" s="2">
-        <v>33678</v>
+        <v>314229</v>
       </c>
       <c r="H8" s="2">
-        <v>32981</v>
+        <v>307053</v>
       </c>
       <c r="I8" s="2">
-        <v>4120</v>
+        <v>48377</v>
       </c>
       <c r="J8" s="2">
-        <v>820</v>
+        <v>11902</v>
       </c>
       <c r="K8" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O8" s="2">
-        <v>62</v>
+        <v>309</v>
       </c>
       <c r="P8" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>69</v>
@@ -1115,10 +1115,10 @@
         <v>72</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1126,49 +1126,49 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>26914</v>
+        <v>113584</v>
       </c>
       <c r="G9" s="2">
-        <v>34833</v>
+        <v>315479</v>
       </c>
       <c r="H9" s="2">
-        <v>34067</v>
+        <v>308397</v>
       </c>
       <c r="I9" s="2">
-        <v>2781</v>
+        <v>33121</v>
       </c>
       <c r="J9" s="2">
-        <v>602</v>
+        <v>8750</v>
       </c>
       <c r="K9" s="2">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="L9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O9" s="2">
-        <v>57</v>
+        <v>563</v>
       </c>
       <c r="P9" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>69</v>
@@ -1177,10 +1177,10 @@
         <v>72</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1188,49 +1188,49 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2">
-        <v>18146</v>
+        <v>108825</v>
       </c>
       <c r="G10" s="2">
-        <v>31216</v>
+        <v>285455</v>
       </c>
       <c r="H10" s="2">
-        <v>30448</v>
+        <v>278294</v>
       </c>
       <c r="I10" s="2">
-        <v>3608</v>
+        <v>20495</v>
       </c>
       <c r="J10" s="2">
-        <v>550</v>
+        <v>6038</v>
       </c>
       <c r="K10" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="L10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O10" s="2">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="P10" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>69</v>
@@ -1239,10 +1239,10 @@
         <v>72</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1250,16 +1250,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F11" s="2">
         <v>5134</v>
@@ -1301,10 +1301,10 @@
         <v>72</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1312,49 +1312,49 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>1098</v>
+        <v>4649</v>
       </c>
       <c r="G12" s="2">
-        <v>1359</v>
+        <v>6316</v>
       </c>
       <c r="H12" s="2">
-        <v>1279</v>
+        <v>6024</v>
       </c>
       <c r="I12" s="2">
-        <v>509</v>
+        <v>2544</v>
       </c>
       <c r="J12" s="2">
-        <v>182</v>
+        <v>909</v>
       </c>
       <c r="K12" s="2">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="L12" s="2">
+        <v>12</v>
+      </c>
+      <c r="M12" s="2">
         <v>2</v>
       </c>
-      <c r="M12" s="2">
-        <v>1</v>
-      </c>
       <c r="N12" s="2">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="O12" s="2">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="P12" s="2">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>69</v>
@@ -1363,10 +1363,10 @@
         <v>72</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1374,49 +1374,49 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>2404</v>
+        <v>3899</v>
       </c>
       <c r="G13" s="2">
-        <v>3408</v>
+        <v>5663</v>
       </c>
       <c r="H13" s="2">
-        <v>3237</v>
+        <v>5345</v>
       </c>
       <c r="I13" s="2">
-        <v>1319</v>
+        <v>2164</v>
       </c>
       <c r="J13" s="2">
-        <v>551</v>
+        <v>910</v>
       </c>
       <c r="K13" s="2">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="L13" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M13" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N13" s="2">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="O13" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="P13" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>69</v>
@@ -1425,10 +1425,10 @@
         <v>72</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1436,25 +1436,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F14" s="2">
         <v>4695</v>
       </c>
       <c r="G14" s="2">
-        <v>6443</v>
+        <v>6444</v>
       </c>
       <c r="H14" s="2">
-        <v>6105</v>
+        <v>6106</v>
       </c>
       <c r="I14" s="2">
         <v>2868</v>
@@ -1487,10 +1487,10 @@
         <v>72</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1498,34 +1498,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F15" s="2">
-        <v>51148</v>
+        <v>66511</v>
       </c>
       <c r="G15" s="2">
-        <v>81062</v>
+        <v>145903</v>
       </c>
       <c r="H15" s="2">
-        <v>78641</v>
+        <v>143921</v>
       </c>
       <c r="I15" s="2">
-        <v>8992</v>
+        <v>9250</v>
       </c>
       <c r="J15" s="2">
-        <v>2677</v>
+        <v>2304</v>
       </c>
       <c r="K15" s="2">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="P15" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>69</v>
@@ -1549,10 +1549,10 @@
         <v>72</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1560,49 +1560,49 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F16" s="2">
-        <v>46442</v>
+        <v>79805</v>
       </c>
       <c r="G16" s="2">
-        <v>75570</v>
+        <v>149012</v>
       </c>
       <c r="H16" s="2">
-        <v>72763</v>
+        <v>146610</v>
       </c>
       <c r="I16" s="2">
-        <v>5453</v>
+        <v>12047</v>
       </c>
       <c r="J16" s="2">
-        <v>1228</v>
+        <v>2443</v>
       </c>
       <c r="K16" s="2">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="L16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O16" s="2">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="P16" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>69</v>
@@ -1611,10 +1611,10 @@
         <v>72</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1622,49 +1622,49 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F17" s="2">
-        <v>50901</v>
+        <v>69196</v>
       </c>
       <c r="G17" s="2">
-        <v>79701</v>
+        <v>144412</v>
       </c>
       <c r="H17" s="2">
-        <v>76787</v>
+        <v>141644</v>
       </c>
       <c r="I17" s="2">
-        <v>14456</v>
+        <v>16763</v>
       </c>
       <c r="J17" s="2">
-        <v>3231</v>
+        <v>3379</v>
       </c>
       <c r="K17" s="2">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="L17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17" s="2">
-        <v>69</v>
+        <v>234</v>
       </c>
       <c r="P17" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>69</v>
@@ -1673,10 +1673,10 @@
         <v>72</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1684,49 +1684,49 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F18" s="2">
-        <v>50740</v>
+        <v>41902</v>
       </c>
       <c r="G18" s="2">
-        <v>80388</v>
+        <v>135941</v>
       </c>
       <c r="H18" s="2">
-        <v>77888</v>
+        <v>133236</v>
       </c>
       <c r="I18" s="2">
-        <v>10122</v>
+        <v>15160</v>
       </c>
       <c r="J18" s="2">
-        <v>2223</v>
+        <v>2440</v>
       </c>
       <c r="K18" s="2">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="L18" s="2">
         <v>0</v>
       </c>
       <c r="M18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O18" s="2">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="P18" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>69</v>
@@ -1735,10 +1735,10 @@
         <v>72</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1746,49 +1746,49 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="2">
-        <v>48958</v>
+        <v>47250</v>
       </c>
       <c r="G19" s="2">
-        <v>76729</v>
+        <v>72398</v>
       </c>
       <c r="H19" s="2">
-        <v>72494</v>
+        <v>70551</v>
       </c>
       <c r="I19" s="2">
-        <v>15101</v>
+        <v>15413</v>
       </c>
       <c r="J19" s="2">
-        <v>2913</v>
+        <v>3307</v>
       </c>
       <c r="K19" s="2">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="L19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2">
         <v>0</v>
       </c>
       <c r="N19" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="P19" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>69</v>
@@ -1797,10 +1797,10 @@
         <v>72</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1808,37 +1808,37 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" s="2">
-        <v>50607</v>
+        <v>45721</v>
       </c>
       <c r="G20" s="2">
-        <v>80866</v>
+        <v>72073</v>
       </c>
       <c r="H20" s="2">
-        <v>77613</v>
+        <v>70233</v>
       </c>
       <c r="I20" s="2">
-        <v>17734</v>
+        <v>12822</v>
       </c>
       <c r="J20" s="2">
-        <v>3927</v>
+        <v>1830</v>
       </c>
       <c r="K20" s="2">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="L20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2">
         <v>1</v>
@@ -1847,22 +1847,208 @@
         <v>6</v>
       </c>
       <c r="O20" s="2">
-        <v>186</v>
+        <v>61</v>
       </c>
       <c r="P20" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="2">
+        <v>43482</v>
+      </c>
+      <c r="G21" s="2">
+        <v>73413</v>
+      </c>
+      <c r="H21" s="2">
+        <v>72424</v>
+      </c>
+      <c r="I21" s="2">
+        <v>9031</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1757</v>
+      </c>
+      <c r="K21" s="2">
+        <v>51</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>5</v>
+      </c>
+      <c r="O21" s="2">
+        <v>80</v>
+      </c>
+      <c r="P21" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G22" s="2">
+        <v>73050</v>
+      </c>
+      <c r="H22" s="2">
+        <v>71722</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6621</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1374</v>
+      </c>
+      <c r="K22" s="2">
+        <v>41</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4</v>
+      </c>
+      <c r="O22" s="2">
+        <v>60</v>
+      </c>
+      <c r="P22" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="2">
+        <v>43967</v>
+      </c>
+      <c r="G23" s="2">
+        <v>70007</v>
+      </c>
+      <c r="H23" s="2">
+        <v>68725</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5993</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1322</v>
+      </c>
+      <c r="K23" s="2">
+        <v>47</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>4</v>
+      </c>
+      <c r="O23" s="2">
+        <v>90</v>
+      </c>
+      <c r="P23" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
